--- a/data/trans_bre/IP1020-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Habitat-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 4,11</t>
+          <t>-1,68; 3,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 7,45</t>
+          <t>-0,33; 7,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 754,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-61,6; —</t>
+          <t>-65,22; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,64</t>
+          <t>-2,76; 1,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,71</t>
+          <t>0,36; 4,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,63</t>
+          <t>-1,51; 2,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 0,7</t>
+          <t>-5,14; 1,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 151,52</t>
+          <t>-86,71; 143,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,69; —</t>
+          <t>-23,98; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,76; 400,42</t>
+          <t>-67,72; 472,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 32,0</t>
+          <t>-79,75; 41,01</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,0</t>
+          <t>-1,64; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,92</t>
+          <t>-0,02; 4,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,24</t>
+          <t>-2,28; 2,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,51</t>
+          <t>-1,14; 5,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,49; 408,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-39,84; 457,46</t>
+          <t>-39,1; 447,91</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,91</t>
+          <t>-1,3; 0,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,91</t>
+          <t>-2,75; 2,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,89</t>
+          <t>-3,46; 0,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 2,09</t>
+          <t>-4,68; 1,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,01; 208,48</t>
+          <t>-73,17; 194,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 213,2</t>
+          <t>-100,0; 164,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,44; 126,27</t>
+          <t>-77,79; 119,84</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,78</t>
+          <t>-0,92; 0,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,48</t>
+          <t>-0,04; 2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,6</t>
+          <t>-1,62; 0,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,88</t>
+          <t>-1,46; 1,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-72,25; 158,21</t>
+          <t>-72,36; 143,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 292,55</t>
+          <t>-10,34; 274,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 61,85</t>
+          <t>-65,28; 51,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 76,63</t>
+          <t>-37,27; 70,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 3,67</t>
+          <t>-2,21; 3,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; -0,44</t>
+          <t>-4,3; -0,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 7,02</t>
+          <t>-0,05; 7,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 754,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-65,22; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,6</t>
+          <t>-2,61; 1,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,31</t>
+          <t>0,31; 4,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,54</t>
+          <t>-1,23; 2,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 1,17</t>
+          <t>-4,98; 0,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,71; 143,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,98; —</t>
+          <t>-39,04; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,72; 472,47</t>
+          <t>-66,02; 397,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,75; 41,01</t>
+          <t>-78,13; 35,7</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,0</t>
+          <t>-1,62; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 4,19</t>
+          <t>-0,02; 4,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 2,23</t>
+          <t>-2,33; 2,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,51</t>
+          <t>-1,06; 5,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-67,45; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-83,49; 408,26</t>
+          <t>-85,62; 378,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 447,91</t>
+          <t>-44,19; 523,14</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,83</t>
+          <t>-1,31; 1,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,74</t>
+          <t>-2,53; 3,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,89</t>
+          <t>-3,45; 1,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,86</t>
+          <t>-4,07; 2,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,17; 194,1</t>
+          <t>-65,77; 239,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 164,17</t>
+          <t>-100,0; 186,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,79; 119,84</t>
+          <t>-77,4; 116,39</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,66</t>
+          <t>-0,81; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,44</t>
+          <t>-0,04; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,57</t>
+          <t>-1,44; 0,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,79</t>
+          <t>-1,59; 1,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-72,36; 143,0</t>
+          <t>-70,82; 135,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 274,72</t>
+          <t>-8,61; 260,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-65,28; 51,53</t>
+          <t>-63,25; 55,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 70,28</t>
+          <t>-41,21; 67,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>228,87%</t>
+          <t>242,73%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,56</t>
+          <t>-1,81; 4,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; -0,44</t>
+          <t>-4,82; -0,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 7,37</t>
+          <t>-0,01; 7,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-64,34; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,09</t>
+          <t>-2,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-42,81%</t>
+          <t>-42,56%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,4</t>
+          <t>-2,74; 1,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,52</t>
+          <t>0,44; 4,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,49</t>
+          <t>-1,46; 2,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 0,91</t>
+          <t>-5,05; 0,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,12; 151,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,04; —</t>
+          <t>-49,69; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 397,85</t>
+          <t>-64,76; 400,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,13; 35,7</t>
+          <t>-76,34; 31,68</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>108,07%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,0</t>
+          <t>-1,56; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 4,26</t>
+          <t>-0,33; 3,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,09</t>
+          <t>-2,04; 2,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 5,72</t>
+          <t>-0,66; 6,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-67,45; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-85,62; 378,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,19; 523,14</t>
+          <t>-26,76; 526,74</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-23,49%</t>
+          <t>-24,05%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,11</t>
+          <t>-1,29; 0,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,15</t>
+          <t>-2,56; 2,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,04</t>
+          <t>-3,3; 0,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 2,05</t>
+          <t>-3,86; 2,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 239,08</t>
+          <t>-67,01; 208,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 186,17</t>
+          <t>-100,0; 213,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,4; 116,39</t>
+          <t>-75,09; 129,12</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,69</t>
+          <t>-0,89; 0,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,55</t>
+          <t>0,1; 2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,65</t>
+          <t>-1,34; 0,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,84</t>
+          <t>-1,34; 2,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,82; 135,01</t>
+          <t>-72,25; 158,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 260,56</t>
+          <t>2,58; 292,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 55,88</t>
+          <t>-62,44; 61,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-41,21; 67,9</t>
+          <t>-33,66; 82,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,187 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>242,73%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.046378818879979</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7116826202791348</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.53625052658852</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.562410170026527</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.4632022904804903</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>2.427299954645427</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,04</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 4,11</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,82; -0,44</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-0,01; 7,95</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-64,34; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.810745543150338</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.820267016949222</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.01097313312089048</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.6434265464364867</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.041432232932307</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.106529927774695</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.4382022355474505</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.945413296940619</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,23</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,11</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-25,94%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>345,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>39,84%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-42,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,74; 1,64</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,44; 4,71</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,46; 2,63</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,05; 0,76</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-79,12; 151,52</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-49,69; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-64,76; 400,42</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-76,34; 31,68</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.5667416686339219</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.229751381747589</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.59471582471479</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.112616490357887</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2594334131542945</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>3.452452280745504</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.3983966106836116</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.4256191899429463</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>253,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>108,07%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.742850006989332</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4392247339942909</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.460081732498563</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.052863591750127</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7912316234404518</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4969235772127151</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.6476125663445327</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7633886375888852</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,56; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,33; 3,92</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,04; 2,24</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 6,97</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-26,76; 526,74</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.637548150060373</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.708459655112132</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.631770835088426</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.7594763842906027</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.515225801350712</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="n">
+        <v>4.004202905337156</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3168019461960729</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +807,283 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-42,13%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-0,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-50,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-24,05%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.3229304870730808</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.701731446756377</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1614061021094629</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.914367432081332</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2.538527949829805</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.1030409032263393</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1.080652115112126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,29; 0,91</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,56; 2,91</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,3; 0,89</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,86; 2,18</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-67,01; 208,48</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 213,2</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-75,09; 129,12</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.560857902767939</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.3283952420397485</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.040702654154502</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.6558972315826882</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
+        <v>-0.2675657908852866</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.923605393254866</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.240851882637927</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.974978106326601</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
+        <v>5.267426954188186</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.2707462068011661</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.01364090524453819</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.087800811213125</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.8864744285282611</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.42132658183215</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.005067454738098154</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.5005922675987763</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2405106987664423</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.29491926374114</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.561110243660785</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.296339676736783</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.859568258083651</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.6700653300821038</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7509120105143805</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9054928743560752</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.91206474406808</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8864538193072838</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.17786064616072</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>2.084792126580826</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.131978326052442</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.291173546843646</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-11,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>84,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-22,83%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; 0,78</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 2,48</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; 0,6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; 2,13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-72,25; 158,21</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,58; 292,55</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-62,44; 61,85</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-33,66; 82,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.101853594215468</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.185675628875601</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.3893560508871737</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.2623625142241598</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1140687109129268</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.8469948233721764</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.2282550770948683</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.07697880987389308</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.888422891794196</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.09830693653064784</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.337781079538165</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.337616091093948</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7225377146048392</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.02584947365055118</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6243521772745275</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3366003518646223</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.7763657359455322</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.478408442990316</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.6014174259371712</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.133175765455143</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.582116715665239</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2.925490288239466</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.6185422157354691</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.8275260690864957</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1091,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
